--- a/data/processing/ola_check.xlsx
+++ b/data/processing/ola_check.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JGOR\Documents\2026\github\FiscalPolicyAnalysis\data\processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CF9675-4E75-4392-897C-24DD70496D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28428B7-74E2-4889-85A1-98DA0AD3CF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28200" windowHeight="14475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10299,7 +10299,7 @@
         <v>25981.348399999999</v>
       </c>
       <c r="C65">
-        <v>179250.9418</v>
+        <v>179170.9638</v>
       </c>
       <c r="D65">
         <f t="shared" si="0"/>
@@ -10307,11 +10307,11 @@
       </c>
       <c r="E65">
         <f t="shared" si="1"/>
-        <v>685261.09499999997</v>
+        <v>685181.11699999997</v>
       </c>
       <c r="F65">
         <f t="shared" si="2"/>
-        <v>13.975460232424242</v>
+        <v>13.977091522795119</v>
       </c>
       <c r="G65">
         <f t="shared" si="3"/>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="H65">
         <f t="shared" si="4"/>
-        <v>1.3682449656072269</v>
+        <v>1.3698762559781041</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -10330,7 +10330,7 @@
         <v>25548.35212</v>
       </c>
       <c r="C66">
-        <v>179675.77069999999</v>
+        <v>179610.45920000001</v>
       </c>
       <c r="D66">
         <f t="shared" si="0"/>
@@ -10338,19 +10338,19 @@
       </c>
       <c r="E66">
         <f t="shared" si="1"/>
-        <v>703161.39450000005</v>
+        <v>703016.1050000001</v>
       </c>
       <c r="F66">
         <f t="shared" si="2"/>
-        <v>14.138728678455609</v>
+        <v>14.141650672426612</v>
       </c>
       <c r="G66">
         <f t="shared" si="3"/>
-        <v>13.257955587537285</v>
+        <v>13.258363410130006</v>
       </c>
       <c r="H66">
         <f t="shared" si="4"/>
-        <v>0.88077309091832312</v>
+        <v>0.88328726229660681</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -10361,7 +10361,7 @@
         <v>27847.954989999998</v>
       </c>
       <c r="C67">
-        <v>185671.34729999999</v>
+        <v>185624.1851</v>
       </c>
       <c r="D67">
         <f t="shared" si="0"/>
@@ -10369,19 +10369,19 @@
       </c>
       <c r="E67">
         <f t="shared" si="1"/>
-        <v>721792.85979999998</v>
+        <v>721600.4081</v>
       </c>
       <c r="F67">
         <f t="shared" si="2"/>
-        <v>14.263962250683365</v>
+        <v>14.267766466635942</v>
       </c>
       <c r="G67">
         <f t="shared" si="3"/>
-        <v>13.727241550853279</v>
+        <v>13.728379871938751</v>
       </c>
       <c r="H67">
         <f t="shared" si="4"/>
-        <v>0.53672069983008619</v>
+        <v>0.53938659469719141</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -10392,7 +10392,7 @@
         <v>25969.18636</v>
       </c>
       <c r="C68">
-        <v>196455.16329999999</v>
+        <v>196401.8849</v>
       </c>
       <c r="D68">
         <f t="shared" si="0"/>
@@ -10400,19 +10400,19 @@
       </c>
       <c r="E68">
         <f t="shared" si="1"/>
-        <v>741053.22310000006</v>
+        <v>740807.49300000002</v>
       </c>
       <c r="F68">
         <f t="shared" si="2"/>
-        <v>14.21582668911544</v>
+        <v>14.220542160471911</v>
       </c>
       <c r="G68">
         <f t="shared" si="3"/>
-        <v>14.036826211943341</v>
+        <v>14.038915587016957</v>
       </c>
       <c r="H68">
         <f t="shared" si="4"/>
-        <v>0.17900047717209944</v>
+        <v>0.18162657345495425</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -10423,7 +10423,7 @@
         <v>28370.37227</v>
       </c>
       <c r="C69">
-        <v>200604.59779999999</v>
+        <v>200405.8419</v>
       </c>
       <c r="D69">
         <f t="shared" si="0"/>
@@ -10431,19 +10431,19 @@
       </c>
       <c r="E69">
         <f t="shared" si="1"/>
-        <v>762406.87910000002</v>
+        <v>762042.37109999999</v>
       </c>
       <c r="F69">
         <f t="shared" si="2"/>
-        <v>14.131019629201031</v>
+        <v>14.137778924875846</v>
       </c>
       <c r="G69">
         <f t="shared" si="3"/>
-        <v>14.148494462669664</v>
+        <v>14.151762705582396</v>
       </c>
       <c r="H69">
         <f t="shared" si="4"/>
-        <v>-1.7474833468632767E-2</v>
+        <v>-1.3983780706549709E-2</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -10454,7 +10454,7 @@
         <v>27376.241190000001</v>
       </c>
       <c r="C70">
-        <v>200381.2867</v>
+        <v>200133.2996</v>
       </c>
       <c r="D70">
         <f t="shared" ref="D70:D79" si="5">SUM(B67:B70)</f>
@@ -10462,19 +10462,19 @@
       </c>
       <c r="E70">
         <f t="shared" ref="E70:E79" si="6">SUM(C67:C70)</f>
-        <v>783112.39510000008</v>
+        <v>782565.21149999998</v>
       </c>
       <c r="F70">
         <f t="shared" ref="F70:F79" si="7">(D70/E70)*100</f>
-        <v>13.99080840701151</v>
+        <v>14.000591030617263</v>
       </c>
       <c r="G70">
         <f t="shared" si="3"/>
-        <v>14.187384311863863</v>
+        <v>14.191934556102577</v>
       </c>
       <c r="H70">
         <f t="shared" si="4"/>
-        <v>-0.19657590485235232</v>
+        <v>-0.19134352548531375</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -10485,7 +10485,7 @@
         <v>29395.435969999999</v>
       </c>
       <c r="C71">
-        <v>203473.8854</v>
+        <v>203402.0172</v>
       </c>
       <c r="D71">
         <f t="shared" si="5"/>
@@ -10493,19 +10493,19 @@
       </c>
       <c r="E71">
         <f t="shared" si="6"/>
-        <v>800914.93320000009</v>
+        <v>800343.04359999998</v>
       </c>
       <c r="F71">
         <f t="shared" si="7"/>
-        <v>13.873038344542129</v>
+        <v>13.882951401715665</v>
       </c>
       <c r="G71">
         <f t="shared" si="3"/>
-        <v>14.150404244002836</v>
+        <v>14.156669645650242</v>
       </c>
       <c r="H71">
         <f t="shared" si="4"/>
-        <v>-0.27736589946070644</v>
+        <v>-0.27371824393457622</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -10516,7 +10516,7 @@
         <v>27951.355279999902</v>
       </c>
       <c r="C72">
-        <v>212953.65150000001</v>
+        <v>212918.7212</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
@@ -10524,19 +10524,19 @@
       </c>
       <c r="E72">
         <f t="shared" si="6"/>
-        <v>817413.42139999999</v>
+        <v>816859.87990000006</v>
       </c>
       <c r="F72">
         <f t="shared" si="7"/>
-        <v>13.835520894225423</v>
+        <v>13.844896474024992</v>
       </c>
       <c r="G72">
         <f t="shared" si="3"/>
-        <v>14.052673267467528</v>
+        <v>14.060465879420171</v>
       </c>
       <c r="H72">
         <f t="shared" si="4"/>
-        <v>-0.21715237324210435</v>
+        <v>-0.2155694053951791</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -10555,19 +10555,19 @@
       </c>
       <c r="E73">
         <f t="shared" si="6"/>
-        <v>830841.92760000005</v>
+        <v>830487.14199999999</v>
       </c>
       <c r="F73">
         <f t="shared" si="7"/>
-        <v>13.955712915805416</v>
+        <v>13.961674821450746</v>
       </c>
       <c r="G73">
         <f t="shared" si="3"/>
-        <v>13.957596818745024</v>
+        <v>13.966554457808442</v>
       </c>
       <c r="H73">
         <f t="shared" si="4"/>
-        <v>-1.883902939608717E-3</v>
+        <v>-4.879636357696171E-3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -10586,19 +10586,19 @@
       </c>
       <c r="E74">
         <f t="shared" si="6"/>
-        <v>843968.93729999999</v>
+        <v>843862.13879999996</v>
       </c>
       <c r="F74">
         <f t="shared" si="7"/>
-        <v>14.083930629042584</v>
+        <v>14.085713079748841</v>
       </c>
       <c r="G74">
         <f t="shared" ref="G74:G79" si="8">AVERAGE(F70:F73)</f>
-        <v>13.913770140396119</v>
+        <v>13.922528431952166</v>
       </c>
       <c r="H74">
         <f t="shared" ref="H74:H79" si="9">F74-G74</f>
-        <v>0.17016048864646471</v>
+        <v>0.1631846477966743</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -10617,19 +10617,19 @@
       </c>
       <c r="E75">
         <f t="shared" si="6"/>
-        <v>859677.01410000003</v>
+        <v>859642.08379999991</v>
       </c>
       <c r="F75">
         <f t="shared" si="7"/>
-        <v>14.102565207809237</v>
+        <v>14.103138244940345</v>
       </c>
       <c r="G75">
         <f t="shared" si="8"/>
-        <v>13.937050695903888</v>
+        <v>13.943808944235062</v>
       </c>
       <c r="H75">
         <f t="shared" si="9"/>
-        <v>0.16551451190534827</v>
+        <v>0.15932930070528251</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -10656,11 +10656,11 @@
       </c>
       <c r="G76">
         <f t="shared" si="8"/>
-        <v>13.994432411720664</v>
+        <v>13.998855655041231</v>
       </c>
       <c r="H76">
         <f t="shared" si="9"/>
-        <v>-0.25062796377782526</v>
+        <v>-0.25505120709839169</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -10671,7 +10671,7 @@
         <v>34099.610679999998</v>
       </c>
       <c r="C77">
-        <v>231004.36369999999</v>
+        <v>230802.61009999999</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
@@ -10679,19 +10679,19 @@
       </c>
       <c r="E77">
         <f t="shared" si="6"/>
-        <v>895234.56050000002</v>
+        <v>895032.80689999997</v>
       </c>
       <c r="F77">
         <f t="shared" si="7"/>
-        <v>13.804149769528474</v>
+        <v>13.807261428553117</v>
       </c>
       <c r="G77">
         <f t="shared" si="8"/>
-        <v>13.971503300150019</v>
+        <v>13.973582648520694</v>
       </c>
       <c r="H77">
         <f t="shared" si="9"/>
-        <v>-0.16735353062154523</v>
+        <v>-0.16632121996757654</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -10702,7 +10702,7 @@
         <v>32288.342259999899</v>
       </c>
       <c r="C78">
-        <v>231094.42509999999</v>
+        <v>231747.84659999999</v>
       </c>
       <c r="D78">
         <f t="shared" si="5"/>
@@ -10710,19 +10710,19 @@
       </c>
       <c r="E78">
         <f t="shared" si="6"/>
-        <v>912820.68920000002</v>
+        <v>913272.35710000014</v>
       </c>
       <c r="F78">
         <f t="shared" si="7"/>
-        <v>13.757086864459284</v>
+        <v>13.750283160738391</v>
       </c>
       <c r="G78">
         <f t="shared" si="8"/>
-        <v>13.933612513580782</v>
+        <v>13.934979300296286</v>
       </c>
       <c r="H78">
         <f t="shared" si="9"/>
-        <v>-0.17652564912149771</v>
+        <v>-0.18469613955789477</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -10733,7 +10733,7 @@
         <v>32957.461490000002</v>
       </c>
       <c r="C79">
-        <v>234696.03409999999</v>
+        <v>235583.08</v>
       </c>
       <c r="D79">
         <f t="shared" si="5"/>
@@ -10741,19 +10741,19 @@
       </c>
       <c r="E79">
         <f t="shared" si="6"/>
-        <v>928334.7611</v>
+        <v>929673.47489999991</v>
       </c>
       <c r="F79">
         <f t="shared" si="7"/>
-        <v>13.655316393602607</v>
+        <v>13.635652973065145</v>
       </c>
       <c r="G79">
         <f t="shared" si="8"/>
-        <v>13.851901572434958</v>
+        <v>13.851121820543673</v>
       </c>
       <c r="H79">
         <f t="shared" si="9"/>
-        <v>-0.19658517883235049</v>
+        <v>-0.21546884747852779</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -10764,7 +10764,7 @@
         <v>30405.96616</v>
       </c>
       <c r="C80">
-        <v>234696.03409999999</v>
+        <v>248872.00390000001</v>
       </c>
       <c r="D80">
         <f t="shared" ref="D80" si="10">SUM(B77:B80)</f>
@@ -10772,19 +10772,19 @@
       </c>
       <c r="E80">
         <f t="shared" ref="E80" si="11">SUM(C77:C80)</f>
-        <v>931490.85700000008</v>
+        <v>947005.54059999995</v>
       </c>
       <c r="F80">
         <f t="shared" ref="F80" si="12">(D80/E80)*100</f>
-        <v>13.929431471596279</v>
+        <v>13.701227186885575</v>
       </c>
       <c r="G80">
         <f t="shared" ref="G80" si="13">AVERAGE(F76:F79)</f>
-        <v>13.7400893688833</v>
+        <v>13.734250502574874</v>
       </c>
       <c r="H80">
         <f t="shared" ref="H80" si="14">F80-G80</f>
-        <v>0.18934210271297935</v>
+        <v>-3.3023315689298727E-2</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -10795,7 +10795,7 @@
         <v>36874.015180000002</v>
       </c>
       <c r="C81">
-        <v>234696.03409999999</v>
+        <v>248377.27040000001</v>
       </c>
       <c r="D81">
         <f t="shared" ref="D81:D82" si="15">SUM(B78:B81)</f>
@@ -10803,19 +10803,19 @@
       </c>
       <c r="E81">
         <f t="shared" ref="E81:E82" si="16">SUM(C78:C81)</f>
-        <v>935182.52740000002</v>
+        <v>964580.20090000005</v>
       </c>
       <c r="F81">
         <f t="shared" ref="F81:F82" si="17">(D81/E81)*100</f>
-        <v>14.171114323366249</v>
+        <v>13.739218881576351</v>
       </c>
       <c r="G81">
         <f t="shared" ref="G81:G82" si="18">AVERAGE(F77:F80)</f>
-        <v>13.786496124796662</v>
+        <v>13.723606187310558</v>
       </c>
       <c r="H81">
         <f t="shared" ref="H81:H82" si="19">F81-G81</f>
-        <v>0.38461819856958712</v>
+        <v>1.5612694265792371E-2</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -10826,7 +10826,7 @@
         <v>37944.29305</v>
       </c>
       <c r="C82">
-        <v>234696.03409999999</v>
+        <v>246494.07199999999</v>
       </c>
       <c r="D82">
         <f t="shared" si="15"/>
@@ -10834,19 +10834,19 @@
       </c>
       <c r="E82">
         <f t="shared" si="16"/>
-        <v>938784.13639999996</v>
+        <v>979326.42629999993</v>
       </c>
       <c r="F82">
         <f t="shared" si="17"/>
-        <v>14.719223570382436</v>
+        <v>14.10987513142736</v>
       </c>
       <c r="G82">
         <f t="shared" si="18"/>
-        <v>13.878237263256105</v>
+        <v>13.706595550566366</v>
       </c>
       <c r="H82">
         <f t="shared" si="19"/>
-        <v>0.8409863071263306</v>
+        <v>0.40327958086099436</v>
       </c>
     </row>
   </sheetData>
@@ -12758,7 +12758,7 @@
         <v>-15074.9</v>
       </c>
       <c r="C65">
-        <v>179250.9418</v>
+        <v>179170.9638</v>
       </c>
       <c r="D65">
         <f t="shared" si="0"/>
@@ -12766,11 +12766,11 @@
       </c>
       <c r="E65">
         <f t="shared" si="1"/>
-        <v>685261.09499999997</v>
+        <v>685181.11699999997</v>
       </c>
       <c r="F65">
         <f t="shared" si="2"/>
-        <v>-1.9550492163136739</v>
+        <v>-1.9552774201014651</v>
       </c>
       <c r="G65">
         <f t="shared" si="3"/>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="H65">
         <f t="shared" si="4"/>
-        <v>-0.43304238416856666</v>
+        <v>-0.43327058795635787</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -12789,7 +12789,7 @@
         <v>-15217.9</v>
       </c>
       <c r="C66">
-        <v>179675.77069999999</v>
+        <v>179610.45920000001</v>
       </c>
       <c r="D66">
         <f t="shared" si="0"/>
@@ -12797,19 +12797,19 @@
       </c>
       <c r="E66">
         <f t="shared" si="1"/>
-        <v>703161.39450000005</v>
+        <v>703016.1050000001</v>
       </c>
       <c r="F66">
         <f t="shared" si="2"/>
-        <v>-2.0691148264539714</v>
+        <v>-2.0695424420611244</v>
       </c>
       <c r="G66">
         <f t="shared" si="3"/>
-        <v>-1.5502383162475257</v>
+        <v>-1.5502953671944737</v>
       </c>
       <c r="H66">
         <f t="shared" si="4"/>
-        <v>-0.51887651020644565</v>
+        <v>-0.51924707486665067</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -12820,7 +12820,7 @@
         <v>-18709.3</v>
       </c>
       <c r="C67">
-        <v>185671.34729999999</v>
+        <v>185624.1851</v>
       </c>
       <c r="D67">
         <f t="shared" si="0"/>
@@ -12828,19 +12828,19 @@
       </c>
       <c r="E67">
         <f t="shared" si="1"/>
-        <v>721792.85979999998</v>
+        <v>721600.4081</v>
       </c>
       <c r="F67">
         <f t="shared" si="2"/>
-        <v>-2.2626597708413634</v>
+        <v>-2.2632632249338664</v>
       </c>
       <c r="G67">
         <f t="shared" si="3"/>
-        <v>-1.7100891366190267</v>
+        <v>-1.7102530914677629</v>
       </c>
       <c r="H67">
         <f t="shared" si="4"/>
-        <v>-0.55257063422233665</v>
+        <v>-0.5530101334661035</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -12851,7 +12851,7 @@
         <v>-15959</v>
       </c>
       <c r="C68">
-        <v>196455.16329999999</v>
+        <v>196401.8849</v>
       </c>
       <c r="D68">
         <f t="shared" si="0"/>
@@ -12859,19 +12859,19 @@
       </c>
       <c r="E68">
         <f t="shared" si="1"/>
-        <v>741053.22310000006</v>
+        <v>740807.49300000002</v>
       </c>
       <c r="F68">
         <f t="shared" si="2"/>
-        <v>-2.191512632798911</v>
+        <v>-2.1922395701254063</v>
       </c>
       <c r="G68">
         <f t="shared" si="3"/>
-        <v>-1.966308313171319</v>
+        <v>-1.9666231315431808</v>
       </c>
       <c r="H68">
         <f t="shared" si="4"/>
-        <v>-0.22520431962759191</v>
+        <v>-0.22561643858222546</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -12882,7 +12882,7 @@
         <v>-10342.9</v>
       </c>
       <c r="C69">
-        <v>200604.59779999999</v>
+        <v>200405.8419</v>
       </c>
       <c r="D69">
         <f t="shared" si="0"/>
@@ -12890,19 +12890,19 @@
       </c>
       <c r="E69">
         <f t="shared" si="1"/>
-        <v>762406.87910000002</v>
+        <v>762042.37109999999</v>
       </c>
       <c r="F69">
         <f t="shared" si="2"/>
-        <v>-1.974965784382047</v>
+        <v>-1.975910470472263</v>
       </c>
       <c r="G69">
         <f t="shared" si="3"/>
-        <v>-2.1195841116019798</v>
+        <v>-2.1200806643054655</v>
       </c>
       <c r="H69">
         <f t="shared" si="4"/>
-        <v>0.14461832721993284</v>
+        <v>0.14417019383320251</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -12913,7 +12913,7 @@
         <v>-8498.4666670000006</v>
       </c>
       <c r="C70">
-        <v>200381.2867</v>
+        <v>200133.2996</v>
       </c>
       <c r="D70">
         <f t="shared" ref="D70:D79" si="5">AVERAGE(B67:B70)</f>
@@ -12921,19 +12921,19 @@
       </c>
       <c r="E70">
         <f t="shared" ref="E70:E79" si="6">SUM(C67:C70)</f>
-        <v>783112.39510000008</v>
+        <v>782565.21149999998</v>
       </c>
       <c r="F70">
         <f t="shared" ref="F70:F79" si="7">(D70/E70)*100</f>
-        <v>-1.7082371254054489</v>
+        <v>-1.7094315553726862</v>
       </c>
       <c r="G70">
         <f t="shared" si="3"/>
-        <v>-2.1245632536190731</v>
+        <v>-2.1252389268981653</v>
       </c>
       <c r="H70">
         <f t="shared" si="4"/>
-        <v>0.41632612821362414</v>
+        <v>0.41580737152547909</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -12944,7 +12944,7 @@
         <v>-9253.3666670000002</v>
       </c>
       <c r="C71">
-        <v>203473.8854</v>
+        <v>203402.0172</v>
       </c>
       <c r="D71">
         <f t="shared" si="5"/>
@@ -12952,19 +12952,19 @@
       </c>
       <c r="E71">
         <f t="shared" si="6"/>
-        <v>800914.93320000009</v>
+        <v>800343.04359999998</v>
       </c>
       <c r="F71">
         <f t="shared" si="7"/>
-        <v>-1.3751065034455772</v>
+        <v>-1.37608909349181</v>
       </c>
       <c r="G71">
         <f t="shared" si="3"/>
-        <v>-2.0343438283569424</v>
+        <v>-2.0352112052260556</v>
       </c>
       <c r="H71">
         <f t="shared" si="4"/>
-        <v>0.65923732491136522</v>
+        <v>0.65912211173424562</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -12975,7 +12975,7 @@
         <v>-11589.93333</v>
       </c>
       <c r="C72">
-        <v>212953.65150000001</v>
+        <v>212918.7212</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
@@ -12983,19 +12983,19 @@
       </c>
       <c r="E72">
         <f t="shared" si="6"/>
-        <v>817413.42139999999</v>
+        <v>816859.87990000006</v>
       </c>
       <c r="F72">
         <f t="shared" si="7"/>
-        <v>-1.2137269105525359</v>
+        <v>-1.2145493872479758</v>
       </c>
       <c r="G72">
         <f t="shared" si="3"/>
-        <v>-1.8124555115079961</v>
+        <v>-1.8134176723655413</v>
       </c>
       <c r="H72">
         <f t="shared" si="4"/>
-        <v>0.59872860095546021</v>
+        <v>0.59886828511756551</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -13014,19 +13014,19 @@
       </c>
       <c r="E73">
         <f t="shared" si="6"/>
-        <v>830841.92760000005</v>
+        <v>830487.14199999999</v>
       </c>
       <c r="F73">
         <f t="shared" si="7"/>
-        <v>-1.1737882592686333</v>
+        <v>-1.1742897037230711</v>
       </c>
       <c r="G73">
         <f t="shared" si="3"/>
-        <v>-1.5680090809464022</v>
+        <v>-1.5689951266461837</v>
       </c>
       <c r="H73">
         <f t="shared" si="4"/>
-        <v>0.39422082167776895</v>
+        <v>0.39470542292311261</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -13045,19 +13045,19 @@
       </c>
       <c r="E74">
         <f t="shared" si="6"/>
-        <v>843968.93729999999</v>
+        <v>843862.13879999996</v>
       </c>
       <c r="F74">
         <f t="shared" si="7"/>
-        <v>-1.2471163966854211</v>
+        <v>-1.2472742307134779</v>
       </c>
       <c r="G74">
         <f t="shared" ref="G74:G79" si="8">AVERAGE(F70:F73)</f>
-        <v>-1.3677146996680487</v>
+        <v>-1.3685899349588857</v>
       </c>
       <c r="H74">
         <f t="shared" ref="H74:H79" si="9">F74-G74</f>
-        <v>0.12059830298262764</v>
+        <v>0.12131570424540783</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -13076,19 +13076,19 @@
       </c>
       <c r="E75">
         <f t="shared" si="6"/>
-        <v>859677.01410000003</v>
+        <v>859642.08379999991</v>
       </c>
       <c r="F75">
         <f t="shared" si="7"/>
-        <v>-1.5948780502295856</v>
+        <v>-1.5949428557687839</v>
       </c>
       <c r="G75">
         <f t="shared" si="8"/>
-        <v>-1.2524345174880418</v>
+        <v>-1.2530506037940836</v>
       </c>
       <c r="H75">
         <f t="shared" si="9"/>
-        <v>-0.34244353274154382</v>
+        <v>-0.3418922519747003</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -13115,11 +13115,11 @@
       </c>
       <c r="G76">
         <f t="shared" si="8"/>
-        <v>-1.307377404184044</v>
+        <v>-1.3077640443633269</v>
       </c>
       <c r="H76">
         <f t="shared" si="9"/>
-        <v>-0.41083739392994767</v>
+        <v>-0.41045075375066475</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -13130,7 +13130,7 @@
         <v>-16054.93333</v>
       </c>
       <c r="C77">
-        <v>231004.36369999999</v>
+        <v>230802.61009999999</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
@@ -13138,19 +13138,19 @@
       </c>
       <c r="E77">
         <f t="shared" si="6"/>
-        <v>895234.56050000002</v>
+        <v>895032.80689999997</v>
       </c>
       <c r="F77">
         <f t="shared" si="7"/>
-        <v>-1.8640142747259367</v>
+        <v>-1.8644344510451489</v>
       </c>
       <c r="G77">
         <f t="shared" si="8"/>
-        <v>-1.4334993760744079</v>
+        <v>-1.4336803970798311</v>
       </c>
       <c r="H77">
         <f t="shared" si="9"/>
-        <v>-0.43051489865152881</v>
+        <v>-0.43075405396531785</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -13161,7 +13161,7 @@
         <v>-21962.2</v>
       </c>
       <c r="C78">
-        <v>231094.42509999999</v>
+        <v>231747.84659999999</v>
       </c>
       <c r="D78">
         <f t="shared" si="5"/>
@@ -13169,19 +13169,19 @@
       </c>
       <c r="E78">
         <f t="shared" si="6"/>
-        <v>912820.68920000002</v>
+        <v>913272.35710000014</v>
       </c>
       <c r="F78">
         <f t="shared" si="7"/>
-        <v>-2.1121654625726465</v>
+        <v>-2.1111208701993895</v>
       </c>
       <c r="G78">
         <f t="shared" si="8"/>
-        <v>-1.6060558799387339</v>
+        <v>-1.6062165839103506</v>
       </c>
       <c r="H78">
         <f t="shared" si="9"/>
-        <v>-0.50610958263391259</v>
+        <v>-0.50490428628903894</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -13192,7 +13192,7 @@
         <v>-28489.866669999999</v>
       </c>
       <c r="C79">
-        <v>234696.03409999999</v>
+        <v>235583.08</v>
       </c>
       <c r="D79">
         <f t="shared" si="5"/>
@@ -13200,19 +13200,19 @@
       </c>
       <c r="E79">
         <f t="shared" si="6"/>
-        <v>928334.7611</v>
+        <v>929673.47489999991</v>
       </c>
       <c r="F79">
         <f t="shared" si="7"/>
-        <v>-2.2517613482156618</v>
+        <v>-2.2485188506371578</v>
       </c>
       <c r="G79">
         <f t="shared" si="8"/>
-        <v>-1.8223181464105402</v>
+        <v>-1.8221782437818286</v>
       </c>
       <c r="H79">
         <f t="shared" si="9"/>
-        <v>-0.42944320180512152</v>
+        <v>-0.42634060685532926</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -13223,7 +13223,7 @@
         <v>-20890.733329999999</v>
       </c>
       <c r="C80">
-        <v>234696.03409999999</v>
+        <v>248872.00390000001</v>
       </c>
       <c r="D80">
         <f t="shared" ref="D80" si="10">AVERAGE(B77:B80)</f>
@@ -13231,19 +13231,19 @@
       </c>
       <c r="E80">
         <f t="shared" ref="E80" si="11">SUM(C77:C80)</f>
-        <v>931490.85700000008</v>
+        <v>947005.54059999995</v>
       </c>
       <c r="F80">
         <f t="shared" ref="F80" si="12">(D80/E80)*100</f>
-        <v>-2.345641201768661</v>
+        <v>-2.3072128298908074</v>
       </c>
       <c r="G80">
         <f t="shared" ref="G80" si="13">AVERAGE(F76:F79)</f>
-        <v>-1.9865389709070593</v>
+        <v>-1.9855722424989219</v>
       </c>
       <c r="H80">
         <f t="shared" ref="H80" si="14">F80-G80</f>
-        <v>-0.35910223086160165</v>
+        <v>-0.3216405873918855</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -13254,7 +13254,7 @@
         <v>-14579.2</v>
       </c>
       <c r="C81">
-        <v>234696.03409999999</v>
+        <v>248377.27040000001</v>
       </c>
       <c r="D81">
         <f t="shared" ref="D81:D82" si="15">AVERAGE(B78:B81)</f>
@@ -13262,19 +13262,19 @@
       </c>
       <c r="E81">
         <f t="shared" ref="E81:E82" si="16">SUM(C78:C81)</f>
-        <v>935182.52740000002</v>
+        <v>964580.20090000005</v>
       </c>
       <c r="F81">
         <f t="shared" ref="F81:F82" si="17">(D81/E81)*100</f>
-        <v>-2.2969312803266559</v>
+        <v>-2.2269273182217146</v>
       </c>
       <c r="G81">
         <f t="shared" ref="G81:G82" si="18">AVERAGE(F77:F80)</f>
-        <v>-2.1433955718207267</v>
+        <v>-2.1328217504431262</v>
       </c>
       <c r="H81">
         <f t="shared" ref="H81:H82" si="19">F81-G81</f>
-        <v>-0.15353570850592924</v>
+        <v>-9.4105567778588473E-2</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -13285,7 +13285,7 @@
         <v>-12703.866669999999</v>
       </c>
       <c r="C82">
-        <v>234696.03409999999</v>
+        <v>246494.07199999999</v>
       </c>
       <c r="D82">
         <f t="shared" si="15"/>
@@ -13293,19 +13293,19 @@
       </c>
       <c r="E82">
         <f t="shared" si="16"/>
-        <v>938784.13639999996</v>
+        <v>979326.42629999993</v>
       </c>
       <c r="F82">
         <f t="shared" si="17"/>
-        <v>-2.0415680159441605</v>
+        <v>-1.9570509028241878</v>
       </c>
       <c r="G82">
         <f t="shared" si="18"/>
-        <v>-2.2516248232209062</v>
+        <v>-2.2234449672372674</v>
       </c>
       <c r="H82">
         <f t="shared" si="19"/>
-        <v>0.21005680727674569</v>
+        <v>0.26639406441307956</v>
       </c>
     </row>
   </sheetData>
